--- a/data/trans_camb/IP18A01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 9,33</t>
+          <t>-8,75; 9,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 9,44</t>
+          <t>-8,28; 9,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,17; -3,6</t>
+          <t>-16,29; -3,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 19,01</t>
+          <t>-1,26; 18,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 7,27</t>
+          <t>-8,85; 6,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 17,18</t>
+          <t>-7,79; 15,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 11,68</t>
+          <t>-1,75; 11,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 5,33</t>
+          <t>-6,12; 5,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 5,82</t>
+          <t>-9,15; 6,05</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,16; 221,5</t>
+          <t>-74,94; 243,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,04; 258,36</t>
+          <t>-66,1; 241,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,58; 770,39</t>
+          <t>-30,3; 814,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,77; 493,29</t>
+          <t>-87,87; 310,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,24 +813,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 262,71</t>
+          <t>-20,6; 231,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,54; 125,36</t>
+          <t>-60,78; 121,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 116,37</t>
+          <t>-100,0; 159,59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 0,09</t>
+          <t>-12,53; -0,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 3,48</t>
+          <t>-10,94; 2,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 28,81</t>
+          <t>-8,08; 25,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 5,25</t>
+          <t>-7,23; 5,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 7,84</t>
+          <t>-5,47; 7,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 7,08</t>
+          <t>-9,94; 7,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 0,74</t>
+          <t>-7,79; 1,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 2,97</t>
+          <t>-6,01; 3,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 13,03</t>
+          <t>-6,97; 11,83</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,41; 11,91</t>
+          <t>-80,09; 11,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-74,76; 58,64</t>
+          <t>-74,77; 29,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 335,91</t>
+          <t>-66,49; 296,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-60,52; 116,19</t>
+          <t>-60,59; 114,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 176,41</t>
+          <t>-52,49; 160,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 153,16</t>
+          <t>-100,0; 164,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 10,49</t>
+          <t>-63,23; 20,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,97; 44,14</t>
+          <t>-51,04; 46,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,2; 156,86</t>
+          <t>-65,33; 131,92</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 9,51</t>
+          <t>-3,4; 11,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 16,19</t>
+          <t>-0,22; 15,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,46; -1,06</t>
+          <t>-10,75; -1,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 19,45</t>
+          <t>4,61; 20,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 13,89</t>
+          <t>-1,23; 12,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 15,22</t>
+          <t>-5,6; 14,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 13,17</t>
+          <t>2,31; 12,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 11,98</t>
+          <t>1,17; 12,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 5,37</t>
+          <t>-5,51; 5,66</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-67,5; 699,85</t>
+          <t>-54,18; 815,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 938,28</t>
+          <t>-25,92; 959,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,82; 1302,81</t>
+          <t>40,27; 1582,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,43; 1004,07</t>
+          <t>-37,87; 885,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,69; 597,1</t>
+          <t>30,36; 586,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 509,91</t>
+          <t>10,69; 604,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 370,29</t>
+          <t>-100,0; 578,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 10,02</t>
+          <t>-3,26; 9,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,96</t>
+          <t>-6,86; 6,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 26,16</t>
+          <t>-7,06; 27,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 8,45</t>
+          <t>-6,1; 8,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 1,84</t>
+          <t>-9,48; 2,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 17,21</t>
+          <t>-8,27; 15,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 7,18</t>
+          <t>-3,5; 6,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 2,01</t>
+          <t>-6,57; 1,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 14,75</t>
+          <t>-5,0; 16,32</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,71; 474,86</t>
+          <t>-47,58; 515,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 376,79</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,2; 276,31</t>
+          <t>-63,68; 260,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 108,25</t>
+          <t>-100,0; 149,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 565,61</t>
+          <t>-100,0; 418,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,76; 190,46</t>
+          <t>-42,95; 177,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-82,96; 71,36</t>
+          <t>-79,97; 67,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 374,82</t>
+          <t>-76,31; 542,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 7,77</t>
+          <t>-12,59; 6,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 5,65</t>
+          <t>-12,96; 5,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,9; -2,08</t>
+          <t>-18,74; -1,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 11,04</t>
+          <t>-7,23; 9,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 13,9</t>
+          <t>-3,8; 12,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 0,0</t>
+          <t>-12,7; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 6,39</t>
+          <t>-6,31; 6,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 7,23</t>
+          <t>-6,43; 7,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -2,09</t>
+          <t>-13,02; -2,98</t>
         </is>
       </c>
     </row>
@@ -1647,29 +1647,29 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 397,22</t>
+          <t>-100,0; 321,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>-88,32; 323,95</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-89,03; —</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-71,65; 251,08</t>
+          <t>-70,44; 337,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-59,37; 274,52</t>
+          <t>-63,53; 282,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 15,49</t>
+          <t>-2,31; 14,71</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,97; 21,21</t>
+          <t>1,65; 22,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 31,16</t>
+          <t>-4,17; 37,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 14,33</t>
+          <t>-2,07; 15,12</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,89; 20,64</t>
+          <t>2,18; 20,5</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 4,24</t>
+          <t>-8,64; 3,92</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 11,52</t>
+          <t>-0,6; 12,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,67; 17,94</t>
+          <t>4,28; 18,04</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 11,96</t>
+          <t>-5,6; 11,15</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 965,87</t>
+          <t>-46,64; 762,09</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1129,6</t>
+          <t>-8,72; 1243,32</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 1625,58</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>-52,01; 792,78</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>4,13; 1259,96</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>-51,44; 776,9</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-7,77; 1190,48</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 389,05</t>
+          <t>-16,89; 456,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>41,95; 642,17</t>
+          <t>42,01; 710,48</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 416,33</t>
+          <t>-100,0; 378,04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,05; 13,24</t>
+          <t>1,39; 13,32</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,75; 16,99</t>
+          <t>4,08; 17,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 17,02</t>
+          <t>-4,67; 17,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 9,88</t>
+          <t>-2,6; 9,8</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,01; 14,89</t>
+          <t>0,29; 14,06</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-12,3; -5,0</t>
+          <t>-13,52; -5,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,81</t>
+          <t>1,47; 9,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,76; 13,46</t>
+          <t>3,8; 13,54</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 3,39</t>
+          <t>-7,38; 3,65</t>
         </is>
       </c>
     </row>
@@ -2079,27 +2079,27 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9,13; 476,64</t>
+          <t>10,73; 421,0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>38,5; 503,52</t>
+          <t>44,93; 482,27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-74,55; 431,68</t>
+          <t>-77,72; 473,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 186,88</t>
+          <t>-24,27; 173,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,75; 264,61</t>
+          <t>1,12; 241,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,15; 193,8</t>
+          <t>14,75; 184,28</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>40,55; 243,6</t>
+          <t>36,25; 251,07</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-90,63; 77,92</t>
+          <t>-89,6; 82,39</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 3,73</t>
+          <t>-9,22; 4,69</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -2,81</t>
+          <t>-14,72; -3,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 4,7</t>
+          <t>-16,5; 5,18</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-13,11; -0,5</t>
+          <t>-14,19; -1,37</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,15; -4,02</t>
+          <t>-15,24; -3,73</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 8,83</t>
+          <t>-15,93; 9,26</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-9,29; -0,27</t>
+          <t>-9,37; -0,66</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-13,14; -4,95</t>
+          <t>-13,54; -5,34</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 2,97</t>
+          <t>-13,44; 2,79</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-47,14; 34,92</t>
+          <t>-47,84; 44,52</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-78,84; -22,5</t>
+          <t>-78,52; -24,21</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 53,23</t>
+          <t>-100,0; 42,98</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-71,58; 0,06</t>
+          <t>-73,37; -10,12</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-82,5; -32,73</t>
+          <t>-81,17; -30,5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 150,79</t>
+          <t>-100,0; 98,45</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-53,68; -1,82</t>
+          <t>-52,81; -4,94</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-74,73; -39,58</t>
+          <t>-75,21; -39,34</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-85,11; 27,71</t>
+          <t>-85,17; 23,56</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 4,01</t>
+          <t>-1,38; 3,93</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,36</t>
+          <t>-1,61; 3,65</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 4,38</t>
+          <t>-5,31; 4,05</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 4,23</t>
+          <t>-1,1; 4,17</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,14</t>
+          <t>-2,17; 2,64</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -0,85</t>
+          <t>-7,22; -0,77</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,17</t>
+          <t>-0,5; 3,23</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,46</t>
+          <t>-1,21; 2,55</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,16</t>
+          <t>-5,37; -0,09</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 56,93</t>
+          <t>-13,44; 54,28</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 47,06</t>
+          <t>-16,57; 49,71</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 57,88</t>
+          <t>-58,42; 55,26</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 60,79</t>
+          <t>-11,48; 57,1</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 44,36</t>
+          <t>-22,69; 38,09</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-76,14; -5,88</t>
+          <t>-76,76; -7,47</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 41,77</t>
+          <t>-5,42; 41,94</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 31,83</t>
+          <t>-13,4; 34,81</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-59,14; -1,87</t>
+          <t>-59,39; -0,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 9,33</t>
+          <t>-7,63; 10,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 9,39</t>
+          <t>-8,24; 8,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -3,63</t>
+          <t>-16,35; -3,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 18,08</t>
+          <t>-1,66; 18,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 6,33</t>
+          <t>-8,62; 6,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 15,81</t>
+          <t>-7,54; 19,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 11,23</t>
+          <t>-2,17; 10,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 5,53</t>
+          <t>-6,09; 5,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 6,05</t>
+          <t>-9,31; 5,04</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,94; 243,6</t>
+          <t>-70,32; 309,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-66,1; 241,47</t>
+          <t>-65,03; 220,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 814,88</t>
+          <t>-28,43; 634,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,87; 310,71</t>
+          <t>-85,64; 361,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 231,81</t>
+          <t>-28,08; 211,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,78; 121,37</t>
+          <t>-59,17; 109,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 159,59</t>
+          <t>-100,0; 143,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,53; -0,06</t>
+          <t>-12,14; -0,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 2,42</t>
+          <t>-10,93; 3,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 25,9</t>
+          <t>-7,34; 29,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 5,71</t>
+          <t>-6,25; 6,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 7,55</t>
+          <t>-5,62; 7,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 7,3</t>
+          <t>-10,03; 8,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 1,29</t>
+          <t>-7,61; 1,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 3,45</t>
+          <t>-6,23; 3,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 11,83</t>
+          <t>-6,65; 12,68</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-80,09; 11,39</t>
+          <t>-81,21; 2,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-74,77; 29,61</t>
+          <t>-74,1; 46,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,49; 296,17</t>
+          <t>-58,69; 345,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-60,59; 114,4</t>
+          <t>-58,18; 122,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 160,51</t>
+          <t>-51,9; 176,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 164,86</t>
+          <t>-100,0; 214,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,23; 20,69</t>
+          <t>-63,05; 20,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,04; 46,09</t>
+          <t>-52,53; 43,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,33; 131,92</t>
+          <t>-60,08; 153,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 11,09</t>
+          <t>-3,62; 10,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 15,99</t>
+          <t>0,4; 15,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -1,06</t>
+          <t>-10,5; -1,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 20,1</t>
+          <t>4,0; 20,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 12,33</t>
+          <t>-0,55; 13,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 14,02</t>
+          <t>-4,7; 17,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 12,61</t>
+          <t>2,2; 12,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 12,0</t>
+          <t>1,31; 11,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 5,66</t>
+          <t>-5,77; 5,3</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 815,74</t>
+          <t>-62,5; 656,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 959,85</t>
+          <t>-19,83; 1091,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40,27; 1582,7</t>
+          <t>23,67; 1604,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 885,91</t>
+          <t>-35,45; 945,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,36; 586,2</t>
+          <t>17,28; 556,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,69; 604,92</t>
+          <t>-0,69; 521,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 578,12</t>
+          <t>-100,0; 458,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 9,91</t>
+          <t>-4,09; 9,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 6,58</t>
+          <t>-6,94; 5,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 27,47</t>
+          <t>-6,95; 27,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 8,4</t>
+          <t>-5,49; 7,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 2,2</t>
+          <t>-9,29; 1,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 15,92</t>
+          <t>-7,75; 16,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 6,21</t>
+          <t>-3,4; 6,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 1,84</t>
+          <t>-6,43; 2,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 16,32</t>
+          <t>-4,49; 14,99</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,58; 515,84</t>
+          <t>-60,45; 485,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 376,79</t>
+          <t>-100,0; 309,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-63,68; 260,38</t>
+          <t>-60,35; 240,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 149,48</t>
+          <t>-100,0; 92,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 418,33</t>
+          <t>-100,0; 480,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,95; 177,4</t>
+          <t>-43,99; 183,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,97; 67,79</t>
+          <t>-79,46; 85,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-76,31; 542,72</t>
+          <t>-72,66; 516,33</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 6,78</t>
+          <t>-12,6; 8,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 5,84</t>
+          <t>-12,26; 6,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,74; -1,98</t>
+          <t>-20,43; -2,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 9,61</t>
+          <t>-6,78; 9,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 12,27</t>
+          <t>-4,12; 13,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 0,0</t>
+          <t>-13,22; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 6,82</t>
+          <t>-6,82; 5,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 7,47</t>
+          <t>-5,87; 6,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,02; -2,98</t>
+          <t>-12,37; -2,12</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 321,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,32; 323,95</t>
+          <t>-88,8; 371,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1667,22 +1667,22 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>-69,4; —</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-70,44; 337,48</t>
+          <t>-70,58; 239,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 282,64</t>
+          <t>-61,71; 258,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 14,71</t>
+          <t>-2,12; 14,44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,65; 22,59</t>
+          <t>1,89; 20,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 37,36</t>
+          <t>-5,39; 36,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 15,12</t>
+          <t>-2,07; 15,73</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,18; 20,5</t>
+          <t>2,23; 20,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 3,92</t>
+          <t>-8,62; 4,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 12,51</t>
+          <t>-0,07; 11,93</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,28; 18,04</t>
+          <t>4,29; 18,12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 11,15</t>
+          <t>-5,14; 10,96</t>
         </is>
       </c>
     </row>
@@ -1863,27 +1863,27 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-46,64; 762,09</t>
+          <t>-39,32; 867,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 1243,32</t>
+          <t>4,04; 1262,44</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1625,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-52,01; 792,78</t>
+          <t>-41,24; 1060,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,13; 1259,96</t>
+          <t>6,01; 1264,56</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 456,56</t>
+          <t>-9,48; 429,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>42,01; 710,48</t>
+          <t>42,92; 644,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 378,04</t>
+          <t>-81,88; 488,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,39; 13,32</t>
+          <t>1,19; 12,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,08; 17,24</t>
+          <t>4,13; 17,42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 17,79</t>
+          <t>-4,82; 20,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 9,8</t>
+          <t>-1,81; 10,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,29; 14,06</t>
+          <t>0,69; 14,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-13,52; -5,03</t>
+          <t>-13,85; -4,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,47; 9,75</t>
+          <t>0,81; 9,89</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,8; 13,54</t>
+          <t>4,33; 13,73</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 3,65</t>
+          <t>-7,03; 4,81</t>
         </is>
       </c>
     </row>
@@ -2079,27 +2079,27 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10,73; 421,0</t>
+          <t>7,88; 351,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>44,93; 482,27</t>
+          <t>41,67; 505,2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-77,72; 473,3</t>
+          <t>-100,0; 565,46</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 173,8</t>
+          <t>-19,67; 182,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,12; 241,88</t>
+          <t>3,29; 253,29</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,75; 184,28</t>
+          <t>5,11; 186,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>36,25; 251,07</t>
+          <t>46,96; 263,1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-89,6; 82,39</t>
+          <t>-88,11; 111,2</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 4,69</t>
+          <t>-8,76; 4,89</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,72; -3,0</t>
+          <t>-14,89; -1,93</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 5,18</t>
+          <t>-16,35; 5,43</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-14,19; -1,37</t>
+          <t>-14,15; -1,63</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,24; -3,73</t>
+          <t>-15,72; -4,53</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 9,26</t>
+          <t>-15,88; 8,92</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -0,66</t>
+          <t>-9,45; -0,21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -5,34</t>
+          <t>-13,02; -4,81</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 2,79</t>
+          <t>-14,23; 3,22</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-47,84; 44,52</t>
+          <t>-47,75; 45,67</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-78,52; -24,21</t>
+          <t>-76,59; -14,09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,98</t>
+          <t>-100,0; 53,25</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-73,37; -10,12</t>
+          <t>-74,39; -9,27</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-81,17; -30,5</t>
+          <t>-83,16; -35,36</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 98,45</t>
+          <t>-100,0; 85,99</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-52,81; -4,94</t>
+          <t>-52,65; -0,79</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-75,21; -39,34</t>
+          <t>-74,89; -37,66</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-85,17; 23,56</t>
+          <t>-86,87; 30,63</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,93</t>
+          <t>-1,71; 3,57</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,65</t>
+          <t>-1,83; 3,57</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,05</t>
+          <t>-5,33; 4,45</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,17</t>
+          <t>-0,77; 4,36</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,64</t>
+          <t>-2,19; 2,88</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -0,77</t>
+          <t>-7,16; -0,83</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,23</t>
+          <t>-0,44; 3,28</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,55</t>
+          <t>-1,1; 2,33</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,37; -0,09</t>
+          <t>-5,48; -0,09</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 54,28</t>
+          <t>-16,84; 49,02</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 49,71</t>
+          <t>-19,13; 50,21</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 55,26</t>
+          <t>-58,45; 60,39</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 57,1</t>
+          <t>-8,2; 63,39</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 38,09</t>
+          <t>-23,21; 41,72</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-76,76; -7,47</t>
+          <t>-78,11; -10,5</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 41,94</t>
+          <t>-4,39; 44,3</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 34,81</t>
+          <t>-12,52; 30,19</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-59,39; -0,63</t>
+          <t>-61,35; -1,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores cuya última consulta médica fue por vacunación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,94</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,64</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-8,48</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,82</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4,23</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>-3,45</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 10,12</t>
+          <t>-0,9; 19,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 8,8</t>
+          <t>-7,9; 7,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,35; -3,59</t>
+          <t>-7,74; 18,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 18,84</t>
+          <t>-8,54; 9,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 6,95</t>
+          <t>-7,75; 9,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 19,02</t>
+          <t>-16,17; -3,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 10,95</t>
+          <t>-2,47; 11,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 5,18</t>
+          <t>-6,42; 5,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 5,04</t>
+          <t>-8,65; 5,74</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121,96%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-14,68%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18,75%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>3,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>7,56%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>121,96%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-14,68%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>56,92%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-45,89%</t>
+          <t>-46,41%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-70,32; 309,2</t>
+          <t>-25,58; 770,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 220,68</t>
+          <t>-82,77; 493,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 634,22</t>
+          <t>-74,16; 221,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,64; 361,17</t>
+          <t>-63,04; 258,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 211,92</t>
+          <t>-27,48; 262,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,17; 109,66</t>
+          <t>-58,54; 125,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 143,2</t>
+          <t>-100,0; 111,38</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-4,22</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-6,23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-4,08</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,52</t>
+          <t>5,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,14; -0,22</t>
+          <t>-6,89; 5,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 3,03</t>
+          <t>-5,38; 7,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 29,56</t>
+          <t>-10,45; 4,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 6,03</t>
+          <t>-13,37; 0,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 7,95</t>
+          <t>-11,44; 3,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 8,73</t>
+          <t>-7,78; 27,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 1,58</t>
+          <t>-8,34; 0,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 3,31</t>
+          <t>-6,76; 2,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 12,68</t>
+          <t>-6,84; 13,18</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-7,09%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-50,91%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-54,1%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-35,4%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53,53%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-7,09%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-42,49%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,21; 2,46</t>
+          <t>-60,52; 116,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-74,1; 46,37</t>
+          <t>-47,63; 176,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,69; 345,6</t>
+          <t>-100,0; 120,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,18; 122,69</t>
+          <t>-83,41; 11,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,9; 176,31</t>
+          <t>-74,76; 58,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 214,35</t>
+          <t>-61,54; 328,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,05; 20,43</t>
+          <t>-65,24; 10,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,53; 43,52</t>
+          <t>-50,97; 44,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,08; 153,07</t>
+          <t>-64,82; 148,91</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,25</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,34</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>7,33</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-4,42</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,25</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,34</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-2,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 10,15</t>
+          <t>3,78; 19,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 15,98</t>
+          <t>-0,6; 13,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,5; -1,05</t>
+          <t>-5,59; 13,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 20,19</t>
+          <t>-3,78; 9,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 13,17</t>
+          <t>-0,45; 16,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 17,29</t>
+          <t>-10,46; -1,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,6</t>
+          <t>2,26; 13,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,89</t>
+          <t>0,94; 11,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 5,3</t>
+          <t>-5,51; 3,86</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>301,51%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>143,03%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>72,36%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>165,91%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>301,51%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>143,03%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>180,47%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-46,85%</t>
+          <t>-53,28%</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,5; 656,51</t>
+          <t>18,82; 1302,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,83; 1091,28</t>
+          <t>-30,43; 1004,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,67; 1604,02</t>
+          <t>-67,5; 699,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 945,08</t>
+          <t>-33,15; 938,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,28; 556,03</t>
+          <t>23,69; 597,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 521,27</t>
+          <t>3,09; 509,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 458,56</t>
+          <t>-100,0; 290,46</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,05</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,72</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,39</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,72</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 9,95</t>
+          <t>-5,63; 8,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 5,92</t>
+          <t>-9,94; 1,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 27,96</t>
+          <t>-7,51; 14,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 7,5</t>
+          <t>-3,82; 10,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 1,69</t>
+          <t>-6,95; 5,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 16,03</t>
+          <t>-6,79; 27,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 6,36</t>
+          <t>-2,62; 7,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,24</t>
+          <t>-6,98; 2,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 14,99</t>
+          <t>-5,14; 15,6</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-56,98%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-5,96%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>54,93%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-11,98%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-56,98%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 485,3</t>
+          <t>-59,2; 276,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 309,61</t>
+          <t>-100,0; 108,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 503,42</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-61,71; 474,86</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-60,35; 240,18</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 92,93</t>
-        </is>
-      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 480,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 183,99</t>
+          <t>-37,76; 190,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,46; 85,08</t>
+          <t>-82,96; 71,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-72,66; 516,33</t>
+          <t>-86,63; 402,46</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,07</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4,46</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,17</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,05</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-2,44</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-8,15</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,46</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-4,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 8,29</t>
+          <t>-5,73; 11,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 6,34</t>
+          <t>-5,1; 13,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,43; -2,02</t>
+          <t>-12,64; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 9,59</t>
+          <t>-12,58; 7,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 13,59</t>
+          <t>-13,66; 5,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 0,0</t>
+          <t>-18,9; -2,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 5,88</t>
+          <t>-6,84; 6,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 6,99</t>
+          <t>-5,79; 7,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,37; -2,12</t>
+          <t>-12,43; -2,09</t>
         </is>
       </c>
     </row>
@@ -1594,27 +1594,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>49,49%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>106,79%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-25,14%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-29,98%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>49,49%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>106,79%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,8; 371,4</t>
+          <t>-89,03; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,14 +1662,14 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 397,22</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-69,4; —</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-70,58; 239,03</t>
+          <t>-71,65; 251,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-61,71; 258,01</t>
+          <t>-59,37; 274,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>5,67</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>10,72</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-3,16</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>5,95</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>10,74</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6,81</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5,67</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,62</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5,8</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>10,72</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-2,78</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,8</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>10,72</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 14,44</t>
+          <t>-2,07; 14,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,89; 20,63</t>
+          <t>1,89; 20,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 36,9</t>
+          <t>-8,66; 3,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 15,73</t>
+          <t>-1,83; 15,49</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,23; 20,16</t>
+          <t>0,97; 21,21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 4,23</t>
+          <t>-5,59; 30,5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 11,93</t>
+          <t>-0,34; 11,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,29; 18,12</t>
+          <t>4,67; 17,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 10,96</t>
+          <t>-5,27; 12,06</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>116,32%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>219,84%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-64,84%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>110,64%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>199,77%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>126,64%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>116,32%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>219,84%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-56,98%</t>
+          <t>104,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 867,69</t>
+          <t>-51,44; 776,9</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4,04; 1262,44</t>
+          <t>-7,77; 1190,48</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-41,24; 1060,39</t>
+          <t>-34,86; 965,87</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6,01; 1264,56</t>
+          <t>-4,0; 1129,6</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 429,75</t>
+          <t>-11,93; 389,05</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>42,92; 644,97</t>
+          <t>41,95; 642,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-81,88; 488,82</t>
+          <t>-87,96; 458,35</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4,09</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>7,38</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-8,35</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>6,91</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>9,9</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,97</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4,09</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>7,38</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-8,35</t>
+          <t>4,04</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,17</t>
+          <t>-2,98</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,19; 12,5</t>
+          <t>-2,43; 9,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,13; 17,42</t>
+          <t>1,01; 14,89</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 20,42</t>
+          <t>-12,3; -5,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 10,71</t>
+          <t>1,05; 13,24</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,69; 14,42</t>
+          <t>3,75; 16,99</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-13,85; -4,92</t>
+          <t>-4,47; 20,69</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,81; 9,89</t>
+          <t>0,96; 9,81</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,33; 13,73</t>
+          <t>3,76; 13,46</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 4,81</t>
+          <t>-7,15; 4,27</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>49,03%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>88,44%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>121,32%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>173,69%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>52,15%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>49,03%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>88,44%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-45,08%</t>
+          <t>-42,42%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,88; 351,42</t>
+          <t>-25,38; 186,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>41,67; 505,2</t>
+          <t>3,75; 264,61</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 565,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 182,91</t>
+          <t>9,13; 476,64</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,29; 253,29</t>
+          <t>38,5; 503,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,43; 532,94</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,11; 186,75</t>
+          <t>8,15; 193,8</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>46,96; 263,1</t>
+          <t>40,55; 243,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-88,11; 111,2</t>
+          <t>-90,93; 98,74</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-7,18</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-9,46</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-7,55</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-1,98</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-8,44</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-8,34</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-7,18</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-9,46</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-7,32</t>
+          <t>-8,74</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-7,7</t>
+          <t>-7,99</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 4,89</t>
+          <t>-13,11; -0,5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,89; -1,93</t>
+          <t>-15,15; -4,02</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 5,43</t>
+          <t>-15,49; 9,82</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-14,15; -1,63</t>
+          <t>-9,11; 3,73</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,72; -4,53</t>
+          <t>-15,05; -2,81</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 8,92</t>
+          <t>-17,07; 3,5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-9,45; -0,21</t>
+          <t>-9,29; -0,27</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-13,02; -4,81</t>
+          <t>-13,14; -4,95</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 3,22</t>
+          <t>-13,67; 3,19</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-48,53%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-63,95%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-51,03%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-13,38%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-57,14%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-56,44%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-48,53%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-63,95%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-49,46%</t>
+          <t>-59,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-52,07%</t>
+          <t>-54,02%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-47,75; 45,67</t>
+          <t>-71,58; 0,06</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-76,59; -14,09</t>
+          <t>-82,5; -32,73</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 53,25</t>
+          <t>-100,0; 151,47</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-74,39; -9,27</t>
+          <t>-47,14; 34,92</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-83,16; -35,36</t>
+          <t>-78,84; -22,5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 85,99</t>
+          <t>-100,0; 47,27</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-52,65; -0,79</t>
+          <t>-53,68; -1,82</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-74,89; -37,66</t>
+          <t>-74,73; -39,58</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-86,87; 30,63</t>
+          <t>-85,23; 28,84</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1,64</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-4,63</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>0,86</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1,64</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-4,3</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-3,06</t>
+          <t>-3,21</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,57</t>
+          <t>-1,02; 4,23</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,57</t>
+          <t>-2,2; 3,14</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,45</t>
+          <t>-7,29; -1,1</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 4,36</t>
+          <t>-1,29; 4,01</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,88</t>
+          <t>-1,65; 3,36</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,16; -0,83</t>
+          <t>-5,57; 4,4</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,28</t>
+          <t>-0,33; 3,17</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,33</t>
+          <t>-1,25; 2,46</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,48; -0,09</t>
+          <t>-5,36; -0,15</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-55,32%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>14,73%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>10,05%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-16,52%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-51,45%</t>
+          <t>-16,26%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-36,23%</t>
+          <t>-38,0%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 49,02</t>
+          <t>-10,9; 60,79</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 50,21</t>
+          <t>-23,1; 44,36</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-58,45; 60,39</t>
+          <t>-77,6; -8,83</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 63,39</t>
+          <t>-13,43; 56,93</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 41,72</t>
+          <t>-16,95; 47,06</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-78,11; -10,5</t>
+          <t>-60,89; 60,05</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 44,3</t>
+          <t>-3,49; 41,77</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 30,19</t>
+          <t>-13,75; 31,83</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-61,35; -1,46</t>
+          <t>-60,72; -2,07</t>
         </is>
       </c>
     </row>
